--- a/artfynd/A 34366-2025 artfynd.xlsx
+++ b/artfynd/A 34366-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -941,6 +941,494 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128427438</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>546859</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6323215</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128462920</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58350</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>546905</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6323071</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128462775</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>546905</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6323071</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128462729</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>546867</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6323145</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34366-2025 artfynd.xlsx
+++ b/artfynd/A 34366-2025 artfynd.xlsx
@@ -946,7 +946,7 @@
         <v>128427438</v>
       </c>
       <c r="B4" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>128462920</v>
       </c>
       <c r="B5" t="n">
-        <v>58350</v>
+        <v>58362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128462775</v>
       </c>
       <c r="B6" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>128462729</v>
       </c>
       <c r="B7" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34366-2025 artfynd.xlsx
+++ b/artfynd/A 34366-2025 artfynd.xlsx
@@ -946,7 +946,7 @@
         <v>128427438</v>
       </c>
       <c r="B4" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>128462920</v>
       </c>
       <c r="B5" t="n">
-        <v>58362</v>
+        <v>58366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128462775</v>
       </c>
       <c r="B6" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>128462729</v>
       </c>
       <c r="B7" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34366-2025 artfynd.xlsx
+++ b/artfynd/A 34366-2025 artfynd.xlsx
@@ -946,7 +946,7 @@
         <v>128427438</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>128462920</v>
       </c>
       <c r="B5" t="n">
-        <v>58366</v>
+        <v>58393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128462775</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>128462729</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34366-2025 artfynd.xlsx
+++ b/artfynd/A 34366-2025 artfynd.xlsx
@@ -946,7 +946,7 @@
         <v>128427438</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>128462920</v>
       </c>
       <c r="B5" t="n">
-        <v>58393</v>
+        <v>58397</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128462775</v>
       </c>
       <c r="B6" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>128462729</v>
       </c>
       <c r="B7" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34366-2025 artfynd.xlsx
+++ b/artfynd/A 34366-2025 artfynd.xlsx
@@ -946,7 +946,7 @@
         <v>128427438</v>
       </c>
       <c r="B4" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>128462920</v>
       </c>
       <c r="B5" t="n">
-        <v>58397</v>
+        <v>58400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128462775</v>
       </c>
       <c r="B6" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>128462729</v>
       </c>
       <c r="B7" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34366-2025 artfynd.xlsx
+++ b/artfynd/A 34366-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1429,6 +1429,129 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129416601</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Flatehult 3:17, Grytsjön, Kråksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>546857</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6323131</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34366-2025 artfynd.xlsx
+++ b/artfynd/A 34366-2025 artfynd.xlsx
@@ -1434,7 +1434,7 @@
         <v>129416601</v>
       </c>
       <c r="B8" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34366-2025 artfynd.xlsx
+++ b/artfynd/A 34366-2025 artfynd.xlsx
@@ -1434,7 +1434,7 @@
         <v>129416601</v>
       </c>
       <c r="B8" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 34366-2025 artfynd.xlsx
+++ b/artfynd/A 34366-2025 artfynd.xlsx
@@ -1434,7 +1434,7 @@
         <v>129416601</v>
       </c>
       <c r="B8" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
